--- a/artfynd/A 32502-2019 artfynd.xlsx
+++ b/artfynd/A 32502-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1716,6 +1716,720 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>114819678</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79504</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Frägnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>488537</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6915894</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114819882</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97535</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Frägnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>488557</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6915834</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>114819297</v>
+      </c>
+      <c r="B13" t="n">
+        <v>95410</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1841</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedflikmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lophozia guttulata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Frägnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>488521</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6915899</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>114819274</v>
+      </c>
+      <c r="B14" t="n">
+        <v>95090</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>53</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Frägnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>488447</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6915961</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>114819275</v>
+      </c>
+      <c r="B15" t="n">
+        <v>95090</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>53</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Frägnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>488489</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6915911</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Via Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>114819864</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78192</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Frägnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>488477</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6915972</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Via Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>114820172</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78103</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>353</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Frägnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>488448</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6915972</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Via Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32502-2019 artfynd.xlsx
+++ b/artfynd/A 32502-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
